--- a/test_output_phase_2_grid.xlsx
+++ b/test_output_phase_2_grid.xlsx
@@ -516,44 +516,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Item No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Rate</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
@@ -562,104 +568,124 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Excavation work</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>NOS</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="F2" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="G2" s="4" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Concrete work</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>NOS</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="F3" s="4" t="n">
         <v>4995</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="G3" s="4" t="n">
         <v>249750</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Steel reinforcement</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>NOS</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>500000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>⚪</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Brick masonry</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>NOS</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>45000</v>
       </c>
     </row>
@@ -726,7 +752,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-01 10:16:20</t>
+          <t>2026-03-01 13:13:57</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -763,7 +789,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-03-01 10:16:20</t>
+          <t>2026-03-01 13:13:57</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
